--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Stock" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Expenses" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Cargo_Companies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stock_Movements" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Product_Costs" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>مدفوع بالكامل</t>
+          <t>قيد التحصيل</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -11339,43 +11339,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DateTime</t>
+          <t>Item_Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Item_Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Operation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Before_Qty</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>After_Qty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Note</t>
+          <t>Unit_Cost</t>
         </is>
       </c>
     </row>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -7872,7 +7872,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P102" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -8018,7 +8018,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P104" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -7726,7 +7726,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P100" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -7628,7 +7628,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P99" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -7555,7 +7555,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P98" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -7336,7 +7336,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P95" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -7288,7 +7288,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P94" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -7215,7 +7215,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P93" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -7069,7 +7069,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P91" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6971,7 +6971,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P90" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6923,7 +6923,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P89" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6777,7 +6777,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P87" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6558,7 +6558,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P84" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6460,7 +6460,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P83" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6412,7 +6412,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6334,7 +6334,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>تم التسليم لشركة الشحن</t>
+          <t>تم تسليم العميل</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6261,7 +6261,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>تم التسليم لشركة الشحن</t>
+          <t>تم تسليم العميل</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6193,7 +6193,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P79" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6095,7 +6095,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P78" t="n">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q143"/>
+  <dimension ref="A1:Q144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10924,6 +10924,79 @@
         <v>1</v>
       </c>
       <c r="Q143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>145</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>هدي</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>92233757</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>مكتب صحار</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>لبانور فراولة معطر 500 مل (الكمية: 1) | لبانور عبق العود معطر 500 مل (الكمية: 5) | لبانور بخور ملكي معطر 500 مل (الكمية: 2) | لبانور شغف معطر 500 مل (الكمية: 1) | لبانور لمسه ملكيه معطر 500 مل (الكمية: 1)</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>12</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>13</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>لم يتم الدفع</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>لم يتم دفع الشحن</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>وصل لي</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>من المكتب (Pickup)</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>قيد التحضير</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>قيد التحصيل</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11098,7 +11171,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -11108,7 +11181,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -11118,7 +11191,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -11128,7 +11201,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -11148,7 +11221,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Expenses" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Cargo_Companies" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Product_Costs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Activity_Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q144"/>
+  <dimension ref="A1:S144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +507,16 @@
           <t>Cargo_Barcode</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Payment_Channel</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Carrier_Collection_Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -579,6 +590,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -652,6 +673,16 @@
         <v>1</v>
       </c>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -725,6 +756,16 @@
         <v>1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -798,6 +839,16 @@
         <v>1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -871,6 +922,16 @@
         <v>1</v>
       </c>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -944,6 +1005,16 @@
         <v>1</v>
       </c>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1017,6 +1088,16 @@
         <v>1</v>
       </c>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1090,6 +1171,16 @@
         <v>1</v>
       </c>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1163,6 +1254,16 @@
         <v>1</v>
       </c>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1236,6 +1337,16 @@
         <v>1</v>
       </c>
       <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1309,6 +1420,16 @@
         <v>1</v>
       </c>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1382,6 +1503,16 @@
         <v>1</v>
       </c>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1455,6 +1586,16 @@
         <v>1</v>
       </c>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1528,6 +1669,16 @@
         <v>1</v>
       </c>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1601,6 +1752,16 @@
         <v>1</v>
       </c>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1674,6 +1835,16 @@
         <v>1</v>
       </c>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1747,6 +1918,16 @@
         <v>1</v>
       </c>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1820,6 +2001,16 @@
         <v>1</v>
       </c>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1893,6 +2084,16 @@
         <v>1</v>
       </c>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1959,13 +2160,23 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>مدفوع بالكامل</t>
+          <t>قيد التحصيل</t>
         </is>
       </c>
       <c r="P21" t="n">
         <v>1</v>
       </c>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2039,6 +2250,16 @@
         <v>1</v>
       </c>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2112,6 +2333,16 @@
         <v>1</v>
       </c>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2185,6 +2416,16 @@
         <v>1</v>
       </c>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2258,6 +2499,16 @@
         <v>1</v>
       </c>
       <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2331,6 +2582,16 @@
         <v>1</v>
       </c>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2404,6 +2665,16 @@
         <v>1</v>
       </c>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2477,6 +2748,16 @@
         <v>1</v>
       </c>
       <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2550,6 +2831,16 @@
         <v>1</v>
       </c>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2616,13 +2907,23 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>مدفوع بالكامل</t>
+          <t>قيد التحصيل</t>
         </is>
       </c>
       <c r="P30" t="n">
         <v>1</v>
       </c>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2696,6 +2997,16 @@
         <v>1</v>
       </c>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2769,6 +3080,16 @@
         <v>1</v>
       </c>
       <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2842,6 +3163,16 @@
         <v>1</v>
       </c>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2915,6 +3246,16 @@
         <v>1</v>
       </c>
       <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2988,6 +3329,16 @@
         <v>1</v>
       </c>
       <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3061,6 +3412,16 @@
         <v>1</v>
       </c>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3134,6 +3495,16 @@
         <v>1</v>
       </c>
       <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3207,6 +3578,16 @@
         <v>1</v>
       </c>
       <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3280,6 +3661,16 @@
         <v>1</v>
       </c>
       <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3353,6 +3744,16 @@
         <v>1</v>
       </c>
       <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3426,6 +3827,16 @@
         <v>1</v>
       </c>
       <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3499,6 +3910,16 @@
         <v>1</v>
       </c>
       <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3572,6 +3993,16 @@
         <v>1</v>
       </c>
       <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3645,6 +4076,16 @@
         <v>1</v>
       </c>
       <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3718,6 +4159,16 @@
         <v>1</v>
       </c>
       <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3791,6 +4242,16 @@
         <v>1</v>
       </c>
       <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3864,6 +4325,16 @@
         <v>1</v>
       </c>
       <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3937,6 +4408,16 @@
         <v>1</v>
       </c>
       <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4010,6 +4491,16 @@
         <v>1</v>
       </c>
       <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4083,6 +4574,16 @@
         <v>1</v>
       </c>
       <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4156,6 +4657,16 @@
         <v>1</v>
       </c>
       <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4229,6 +4740,16 @@
         <v>1</v>
       </c>
       <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4302,6 +4823,16 @@
         <v>1</v>
       </c>
       <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4375,6 +4906,16 @@
         <v>1</v>
       </c>
       <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4448,6 +4989,16 @@
         <v>1</v>
       </c>
       <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4521,6 +5072,16 @@
         <v>1</v>
       </c>
       <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4594,6 +5155,16 @@
         <v>1</v>
       </c>
       <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4667,6 +5238,16 @@
         <v>1</v>
       </c>
       <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4740,6 +5321,16 @@
         <v>1</v>
       </c>
       <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4813,6 +5404,16 @@
         <v>1</v>
       </c>
       <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4886,6 +5487,16 @@
         <v>1</v>
       </c>
       <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4959,6 +5570,16 @@
         <v>1</v>
       </c>
       <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5032,6 +5653,16 @@
         <v>1</v>
       </c>
       <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5105,6 +5736,16 @@
         <v>1</v>
       </c>
       <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5178,6 +5819,16 @@
         <v>1</v>
       </c>
       <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5251,6 +5902,16 @@
         <v>1</v>
       </c>
       <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5324,6 +5985,16 @@
         <v>1</v>
       </c>
       <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5397,6 +6068,16 @@
         <v>1</v>
       </c>
       <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5463,13 +6144,23 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>مدفوع بالكامل</t>
+          <t>قيد التحصيل</t>
         </is>
       </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
       <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5543,6 +6234,16 @@
         <v>1</v>
       </c>
       <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5616,6 +6317,16 @@
         <v>1</v>
       </c>
       <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5689,6 +6400,16 @@
         <v>1</v>
       </c>
       <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5755,13 +6476,23 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>مدفوع بالكامل</t>
+          <t>قيد التحصيل</t>
         </is>
       </c>
       <c r="P73" t="n">
         <v>1</v>
       </c>
       <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5835,6 +6566,16 @@
         <v>1</v>
       </c>
       <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5908,6 +6649,16 @@
         <v>1</v>
       </c>
       <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5974,13 +6725,23 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P76" t="n">
         <v>1</v>
       </c>
       <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6047,13 +6808,23 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P77" t="n">
         <v>1</v>
       </c>
       <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6127,6 +6898,16 @@
         <v>1</v>
       </c>
       <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6200,6 +6981,16 @@
         <v>1</v>
       </c>
       <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6273,6 +7064,16 @@
         <v>1</v>
       </c>
       <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6339,13 +7140,23 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P81" t="n">
         <v>1</v>
       </c>
       <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6419,6 +7230,16 @@
         <v>1</v>
       </c>
       <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6492,6 +7313,16 @@
         <v>1</v>
       </c>
       <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6565,6 +7396,16 @@
         <v>1</v>
       </c>
       <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6631,13 +7472,23 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P85" t="n">
         <v>1</v>
       </c>
       <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6704,13 +7555,23 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P86" t="n">
         <v>1</v>
       </c>
       <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6784,6 +7645,16 @@
         <v>1</v>
       </c>
       <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6850,13 +7721,23 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P88" t="n">
         <v>1</v>
       </c>
       <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6930,6 +7811,16 @@
         <v>1</v>
       </c>
       <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7003,6 +7894,16 @@
         <v>1</v>
       </c>
       <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7076,6 +7977,16 @@
         <v>1</v>
       </c>
       <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7149,6 +8060,16 @@
         <v>1</v>
       </c>
       <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7222,6 +8143,16 @@
         <v>1</v>
       </c>
       <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7295,6 +8226,16 @@
         <v>1</v>
       </c>
       <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7368,6 +8309,16 @@
         <v>1</v>
       </c>
       <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7441,6 +8392,16 @@
         <v>1</v>
       </c>
       <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7514,6 +8475,16 @@
         <v>1</v>
       </c>
       <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7587,6 +8558,16 @@
         <v>1</v>
       </c>
       <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7660,6 +8641,16 @@
         <v>1</v>
       </c>
       <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7733,6 +8724,16 @@
         <v>1</v>
       </c>
       <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7806,6 +8807,16 @@
         <v>1</v>
       </c>
       <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7879,6 +8890,16 @@
         <v>1</v>
       </c>
       <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7952,6 +8973,16 @@
         <v>1</v>
       </c>
       <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8025,6 +9056,16 @@
         <v>1</v>
       </c>
       <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8066,7 +9107,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -8091,13 +9132,23 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P105" t="n">
         <v>1</v>
       </c>
       <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8171,6 +9222,16 @@
         <v>1</v>
       </c>
       <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8244,6 +9305,16 @@
         <v>1</v>
       </c>
       <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8317,6 +9388,16 @@
         <v>1</v>
       </c>
       <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8390,6 +9471,16 @@
         <v>1</v>
       </c>
       <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8463,6 +9554,16 @@
         <v>1</v>
       </c>
       <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8536,6 +9637,16 @@
         <v>1</v>
       </c>
       <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8609,6 +9720,16 @@
         <v>1</v>
       </c>
       <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8682,6 +9803,16 @@
         <v>1</v>
       </c>
       <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8755,6 +9886,16 @@
         <v>1</v>
       </c>
       <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8828,6 +9969,16 @@
         <v>1</v>
       </c>
       <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8901,6 +10052,16 @@
         <v>1</v>
       </c>
       <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8974,6 +10135,16 @@
         <v>1</v>
       </c>
       <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9047,6 +10218,16 @@
         <v>1</v>
       </c>
       <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9120,6 +10301,16 @@
         <v>1</v>
       </c>
       <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9193,6 +10384,16 @@
         <v>0</v>
       </c>
       <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9266,6 +10467,16 @@
         <v>0</v>
       </c>
       <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9339,6 +10550,16 @@
         <v>0</v>
       </c>
       <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9412,6 +10633,16 @@
         <v>1</v>
       </c>
       <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9485,6 +10716,16 @@
         <v>1</v>
       </c>
       <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9558,6 +10799,16 @@
         <v>1</v>
       </c>
       <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9631,6 +10882,16 @@
         <v>1</v>
       </c>
       <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9708,6 +10969,16 @@
           <t>13738399.0</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9785,6 +11056,16 @@
           <t>13738398.0</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -9862,6 +11143,16 @@
           <t>13738397.0</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9939,6 +11230,16 @@
           <t>13738396.0</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10016,6 +11317,16 @@
           <t>13738395.0</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10093,6 +11404,16 @@
           <t>13738394.0</t>
         </is>
       </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10170,6 +11491,16 @@
           <t>13738393.0</t>
         </is>
       </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10247,6 +11578,16 @@
           <t>13738392.0</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10324,6 +11665,16 @@
           <t>13738391.0</t>
         </is>
       </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10401,6 +11752,16 @@
           <t>13738390.0</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10478,6 +11839,16 @@
           <t>13738389.0</t>
         </is>
       </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10555,6 +11926,16 @@
           <t>13738388.0</t>
         </is>
       </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10632,6 +12013,16 @@
           <t>13738387.0</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10705,6 +12096,16 @@
         <v>1</v>
       </c>
       <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -10778,6 +12179,16 @@
         <v>1</v>
       </c>
       <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10844,13 +12255,23 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P142" t="n">
         <v>2</v>
       </c>
       <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10917,13 +12338,23 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P143" t="n">
         <v>1</v>
       </c>
       <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>دفع مباشر إلى لبانور</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>تم الدفع مسبقاً</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10997,6 +12428,16 @@
         <v>2</v>
       </c>
       <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11430,4 +12871,82 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>User_Role</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Session_ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Connection_Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-30 22:50:36</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01b10c09-359</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 143 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -6783,7 +6783,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>تم الدفع</t>
+          <t>لم يتم الدفع</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>مدفوع بالكامل</t>
+          <t>قيد التحصيل</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6817,12 +6817,12 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>دفع مباشر إلى لبانور</t>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>تم الدفع مسبقاً</t>
+          <t>قيد التحصيل من شركة الشحن</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12946,6 +12946,38 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-30 22:52:06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>01b10c09-359</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 143 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -7716,7 +7716,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>تم التسليم لشركة الشحن</t>
+          <t>تم تسليم العميل</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -12879,7 +12879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12978,6 +12978,38 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-30 22:55:02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01b10c09-359</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 143 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -10103,7 +10103,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>تم التسليم لشركة الشحن</t>
+          <t>تم تسليم العميل</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -10137,12 +10137,12 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+          <t>تحصيل عبر شركة الشحن</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>قيد التحصيل من شركة الشحن</t>
+          <t>تم التحصيل من شركة الشحن</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13010,6 +13010,38 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:08:12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 143 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -9273,7 +9273,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>تم التسليم لشركة الشحن</t>
+          <t>تم تسليم العميل</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -9307,12 +9307,12 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+          <t>تحصيل عبر شركة الشحن</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>قيد التحصيل من شركة الشحن</t>
+          <t>تم التحصيل من شركة الشحن</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13042,6 +13042,38 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:08:49</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 143 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -9522,7 +9522,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>تم التسليم لشركة الشحن</t>
+          <t>تم تسليم العميل</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -9556,12 +9556,12 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+          <t>تحصيل عبر شركة الشحن</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>قيد التحصيل من شركة الشحن</t>
+          <t>تم التحصيل من شركة الشحن</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13074,6 +13074,38 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:11:31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 143 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -9937,7 +9937,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>تم التسليم لشركة الشحن</t>
+          <t>تم تسليم العميل</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9971,12 +9971,12 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+          <t>تحصيل عبر شركة الشحن</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>قيد التحصيل من شركة الشحن</t>
+          <t>تم التحصيل من شركة الشحن</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13106,6 +13106,38 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:12:12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 143 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -9605,7 +9605,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>تم التسليم لشركة الشحن</t>
+          <t>تم تسليم العميل</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -9639,12 +9639,12 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+          <t>تحصيل عبر شركة الشحن</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>قيد التحصيل من شركة الشحن</t>
+          <t>تم التحصيل من شركة الشحن</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13138,6 +13138,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:12:50</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 143 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -9688,7 +9688,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>لم يتم الدفع</t>
+          <t>تم الدفع</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>تم التسليم لشركة الشحن</t>
+          <t>تم تسليم العميل</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>قيد التحصيل</t>
+          <t>مدفوع بالكامل</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -9722,12 +9722,12 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+          <t>تحصيل عبر شركة الشحن</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>قيد التحصيل من شركة الشحن</t>
+          <t>تم التحصيل من شركة الشحن</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13170,6 +13170,38 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:12:57</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 143 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S144"/>
+  <dimension ref="A1:S145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12434,6 +12434,89 @@
         </is>
       </c>
       <c r="S144" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>146</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>فاطمه وجب</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>92089600</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>مكتب صلاله</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>لبانور عبق العود معطر 500 مل (الكمية: 1) | لبانور شغف معطر 500 مل (الكمية: 1) | لبانور بخور ملكي معطر 500 مل (الكمية: 1) | لبانور خوخ معطر 500 مل (الكمية: 1)</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>6</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="n">
+        <v>7</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>لم يتم الدفع</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>لم يتم دفع الشحن</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>وصل لي</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>من المكتب (Pickup)</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>قيد التحضير</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>قيد التحصيل</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
         <is>
           <t>قيد التحصيل من شركة الشحن</t>
         </is>
@@ -12612,7 +12695,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -12622,7 +12705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -12642,7 +12725,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -12652,7 +12735,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -12879,7 +12962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13202,6 +13285,38 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:19:12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 144 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -12962,7 +12962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13317,6 +13317,38 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:24:28</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 144 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -12962,7 +12962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13349,6 +13349,38 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:24:38</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 144 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -12715,7 +12715,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -12962,7 +12962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13381,6 +13381,38 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:27:47</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 144 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -12465,7 +12465,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>لبانور عبق العود معطر 500 مل (الكمية: 1) | لبانور شغف معطر 500 مل (الكمية: 1) | لبانور بخور ملكي معطر 500 مل (الكمية: 1) | لبانور خوخ معطر 500 مل (الكمية: 1)</t>
+          <t>لبانور عبق العود معطر 500 مل (الكمية: 1) | لبانور شغف معطر 500 مل (الكمية: 1) | لبانور بخور ملكي معطر 500 مل (الكمية: 1) | لبانور خوخ معطر 500 مل (الكمية: 1) | لبانور لمسه ملكيه معطر 500 مل (الكمية: 1)</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -12715,7 +12715,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -12962,7 +12962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13413,6 +13413,38 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:28:33</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 144 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S145"/>
+  <dimension ref="A1:S146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12517,6 +12517,89 @@
         </is>
       </c>
       <c r="S145" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>147</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Aidan alnoubi</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>93690292</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>مكتب صلاله</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>لبانور شغف معطر 500 مل (الكمية: 2) | لبانور خوخ معطر 500 مل (الكمية: 2) | لبانور لمسه ملكيه معطر 500 مل (الكمية: 2) | لبانور فراولة معطر 500 مل (الكمية: 2) | لبانور بخور ملكي معطر 500 مل (الكمية: 2)</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>12</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>13</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>لم يتم الدفع</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>لم يتم دفع الشحن</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>وصل لي</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>من المكتب (Pickup)</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>قيد التحضير</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>قيد التحصيل</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
         <is>
           <t>قيد التحصيل من شركة الشحن</t>
         </is>
@@ -12695,7 +12778,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -12705,7 +12788,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -12715,7 +12798,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -12735,7 +12818,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -12745,7 +12828,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -12962,7 +13045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13445,6 +13528,38 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:34:35</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>c145579a-c39</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 145 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/system_database.xlsx
+++ b/system_database.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S146"/>
+  <dimension ref="A1:S147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12600,6 +12600,89 @@
         </is>
       </c>
       <c r="S146" t="inlineStr">
+        <is>
+          <t>قيد التحصيل من شركة الشحن</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>148</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ام لؤي</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>95238385</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>مكتب العامراتخوخ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>لبانور خوخ معطر 500 مل (الكمية: 1) | لبانور لمسه ملكيه معطر 500 مل (الكمية: 1) | لبانور شغف معطر 500 مل (الكمية: 1) | لبانور فراولة معطر 500 مل (الكمية: 1) | لبانور عبق العود معطر 500 مل (الكمية: 1)</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>6</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="n">
+        <v>7</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>لم يتم الدفع</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>لم يتم دفع الشحن</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>وصل لي</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>من المكتب (Pickup)</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>قيد التحضير</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>قيد التحصيل</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>تحصيل عند الاستلام عبر شركة الشحن</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
         <is>
           <t>قيد التحصيل من شركة الشحن</t>
         </is>
@@ -12788,7 +12871,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -12798,7 +12881,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -12808,7 +12891,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -12818,7 +12901,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -12828,7 +12911,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -13045,7 +13128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13560,6 +13643,38 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:43:59</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>456ccd5a-555</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>حفظ معاملة / تحديث قاعدة البيانات</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>عدد الفواتير: 146 | عدد أصناف المخزون: 28 | المصروفات: 0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>جارٍ مزامنة GitHub</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
